--- a/diseases/d106/1995-1999.xlsx
+++ b/diseases/d106/1995-1999.xlsx
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18691,7 +18691,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22930,7 +22930,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23730,7 +23730,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -25330,7 +25330,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -26930,7 +26930,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -27730,7 +27730,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -29330,7 +29330,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -30130,7 +30130,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -31169,7 +31169,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32769,7 +32769,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -33569,7 +33569,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -34369,7 +34369,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35969,7 +35969,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36769,7 +36769,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -37569,7 +37569,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -39169,7 +39169,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39969,7 +39969,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -41008,7 +41008,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -41808,7 +41808,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -42608,7 +42608,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -43408,7 +43408,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -44208,7 +44208,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -45008,7 +45008,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -45808,7 +45808,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -46608,7 +46608,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -47408,7 +47408,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -48208,7 +48208,7 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -49808,7 +49808,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">

--- a/diseases/d106/1995-1999.xlsx
+++ b/diseases/d106/1995-1999.xlsx
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18691,7 +18691,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22930,7 +22930,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23730,7 +23730,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -25330,7 +25330,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -26930,7 +26930,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -27730,7 +27730,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -29330,7 +29330,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -30130,7 +30130,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -31169,7 +31169,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32769,7 +32769,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -33569,7 +33569,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -34369,7 +34369,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35969,7 +35969,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36769,7 +36769,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -37569,7 +37569,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -39169,7 +39169,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39969,7 +39969,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -41008,7 +41008,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -41808,7 +41808,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -42608,7 +42608,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -43408,7 +43408,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -44208,7 +44208,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -45008,7 +45008,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -45808,7 +45808,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -46608,7 +46608,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -47408,7 +47408,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -48208,7 +48208,7 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -49008,7 +49008,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -49808,7 +49808,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
